--- a/automotive_forms/010_used_car_monthly_payment_inquiry_form--automotive_forms.xlsx
+++ b/automotive_forms/010_used_car_monthly_payment_inquiry_form--automotive_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,40 +515,40 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>used_car_monthly_payment_inquiry_form_page_1</t>
+          <t>page_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Used Car Monthly Payment Inquiry Form</t>
+          <t>Used Car Financing Inquiry</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2</t>
+          <t>page_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Used Car Information</t>
+          <t>Vehicle Information</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2</t>
+          <t>page_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>used-car-vehicle-make</t>
+          <t>Vehicle Year</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2</t>
+          <t>page_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>used-car-vehicle-year</t>
+          <t>Vehicle Mileage</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2</t>
+          <t>page_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>used-car-vehicle-year</t>
+          <t>Vehicle Price</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2</t>
+          <t>page_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>used-car-vehicle-mileage</t>
+          <t>Monthly Payment Preference</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2</t>
+          <t>page_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>used-car-vehicle-price</t>
+          <t>Contact Information</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2</t>
+          <t>page_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>used-car-monthly-payment</t>
+          <t>Page 8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2</t>
+          <t>page_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>contact-email</t>
+          <t>Follow-up Appointment</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2</t>
+          <t>page_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>contact-phone</t>
+          <t>Follow-up Appointment Time</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2</t>
+          <t>page_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>used_car_monthly_payment_inquiry_form_comments</t>
+          <t>Follow-up Appointment Location</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,322 +768,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2</t>
+          <t>page_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>follow-up-appointment-preference</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>follow-up-appointment-preferred-day-and-time</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>follow-up-appointment-preferred-day-and-time</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
           <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>follow-up-appointment-preferred-time</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>used-car-monthly-payment-inquiry-form-submission</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>used-car-monthly-payment-inquiry-form-submission</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>used-car-monthly-payment-inquiry-form-submission</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>used-car-monthly-payment-inquiry-form-submission</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>follow-up-appointment-preferred-method</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>follow-up-appointment-preferred-location</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>follow-up-appointment-preferred-location</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>used_car_monthly_payment_inquiry_form_comments</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>follow-up-appointment-preferred-method</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>follow-up-appointment-preferred-time</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,459 +827,238 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2_choices</t>
+          <t>page_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'used_car_financing_options',_'label':_'used_car_financing_options'}</t>
+          <t>used_car_financing_options</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Used Car Financing Options', 'label': 'Used Car Financing Options'}</t>
+          <t>Used Car Financing Options</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2_choices</t>
+          <t>page_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'used_car_lease_options',_'label':_'used_car_lease_options'}</t>
+          <t>used_car_lease_options</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Used Car Lease Options', 'label': 'Used Car Lease Options'}</t>
+          <t>Used Car Lease Options</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2_choices</t>
+          <t>page_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2_choices</t>
+          <t>page_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'toyota',_'label':_'toyota'}</t>
+          <t>toyota</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Toyota', 'label': 'Toyota'}</t>
+          <t>Toyota</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2_choices</t>
+          <t>page_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'honda',_'label':_'honda'}</t>
+          <t>honda</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Honda', 'label': 'Honda'}</t>
+          <t>Honda</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2_choices</t>
+          <t>page_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'volkswagen',_'label':_'volkswagen'}</t>
+          <t>volkswagen</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Volkswagen', 'label': 'Volkswagen'}</t>
+          <t>Volkswagen</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2_choices</t>
+          <t>page_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2_choices</t>
+          <t>page_6_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'phone',_'label':_'phone'}</t>
+          <t>lowest_price_first</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Phone', 'label': 'Phone'}</t>
+          <t>Lowest Price First</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2_choices</t>
+          <t>page_6_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'email',_'label':_'email'}</t>
+          <t>highest_price_first</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Email', 'label': 'Email'}</t>
+          <t>Highest Price First</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2_choices</t>
+          <t>page_6_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'in_person',_'label':_'in_person'}</t>
+          <t>best_interest_rate</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'In Person', 'label': 'In Person'}</t>
+          <t>Best Interest Rate</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2_choices</t>
+          <t>page_9_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Other', 'label': 'Other'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2_choices</t>
+          <t>page_9_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2_choices</t>
+          <t>page_9_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>in_person</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>In Person</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2_choices</t>
+          <t>page_9_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>{'value':_false,_'label':_false}</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>{'value': False, 'label': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>{'value':_true,_'label':_true}</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>{'value': True, 'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>{'value':_false,_'label':_false}</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>{'value': False, 'label': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>{'value':_true,_'label':_true}</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>{'value': True, 'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>{'value':_false,_'label':_false}</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>{'value': False, 'label': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>{'value':_'phone',_'label':_'phone'}</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>{'value': 'Phone', 'label': 'Phone'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>{'value':_'email',_'label':_'email'}</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>{'value': 'Email', 'label': 'Email'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>{'value':_'in_person',_'label':_'in_person'}</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>{'value': 'In Person', 'label': 'In Person'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>{'value': 'Other', 'label': 'Other'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>{'value':_'phone',_'label':_'phone'}</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>{'value': 'Phone', 'label': 'Phone'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>{'value':_'email',_'label':_'email'}</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>{'value': 'Email', 'label': 'Email'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>{'value':_'in_person',_'label':_'in_person'}</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>{'value': 'In Person', 'label': 'In Person'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>used_car_monthly_payment_inquiry_form_page_2_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>{'value': 'Other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
